--- a/data/cint_panelbook.xlsx
+++ b/data/cint_panelbook.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EA5"/>
+  <dimension ref="A1:EA6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2672,6 +2672,403 @@
         <v>17846</v>
       </c>
       <c r="EA5" t="n">
+        <v>5199</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2173</v>
+      </c>
+      <c r="C6" t="n">
+        <v>28516</v>
+      </c>
+      <c r="D6" t="n">
+        <v>9493</v>
+      </c>
+      <c r="E6" t="n">
+        <v>780092</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4457673</v>
+      </c>
+      <c r="G6" t="n">
+        <v>865895</v>
+      </c>
+      <c r="H6" t="n">
+        <v>6716</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1496</v>
+      </c>
+      <c r="J6" t="n">
+        <v>14755</v>
+      </c>
+      <c r="K6" t="n">
+        <v>15812</v>
+      </c>
+      <c r="L6" t="n">
+        <v>20282</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1278943</v>
+      </c>
+      <c r="N6" t="n">
+        <v>50</v>
+      </c>
+      <c r="O6" t="n">
+        <v>17533</v>
+      </c>
+      <c r="P6" t="n">
+        <v>20915</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3951</v>
+      </c>
+      <c r="R6" t="n">
+        <v>3595316</v>
+      </c>
+      <c r="S6" t="n">
+        <v>253796</v>
+      </c>
+      <c r="T6" t="n">
+        <v>97</v>
+      </c>
+      <c r="U6" t="n">
+        <v>9639</v>
+      </c>
+      <c r="V6" t="n">
+        <v>5683167</v>
+      </c>
+      <c r="W6" t="n">
+        <v>736724</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2405488</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>729952</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>112207</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>230228</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>9251</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>531470</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>2413</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>538220</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>73756</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>146373</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>334641</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>30882</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>90542</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>703</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>15270</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1250397</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>6348389</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>278</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>10912450</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>43566</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>816924</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>117534</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>428</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>29699</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>420736</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>549915</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1292</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>3384498</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1364615</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>8489</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>785595</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>92652</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>5148664</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>20436</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>8467</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>2521220</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>28594</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>54434</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>233666</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>41005</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>98223</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>6097</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>912</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>107</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>352</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>190783</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>9062</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>1870</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>807408</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>3189</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>571</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>3464778</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>11489</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>1138</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>154364</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>8970</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>1880</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>8641</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>3000670</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>508629</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>15341</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>381183</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>302</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>640823</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>19578</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>104474</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>298</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>56991</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>14366</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>479437</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>996816</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>2333142</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>994348</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>46067</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>46099</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>864144</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>1720</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>1201858</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>20980</v>
+      </c>
+      <c r="CY6" t="n">
+        <v>207047</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>217</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>919396</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>255876</v>
+      </c>
+      <c r="DC6" t="n">
+        <v>131073</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>1373616</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>1009355</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>4230879</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>29660</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>233</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>2832982</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>640281</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>459221</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>17588</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>961746</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>16473</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>1127970</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>17511</v>
+      </c>
+      <c r="DQ6" t="n">
+        <v>249555</v>
+      </c>
+      <c r="DR6" t="n">
+        <v>746758</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>22982706</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>77339497</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>69906</v>
+      </c>
+      <c r="DV6" t="n">
+        <v>406</v>
+      </c>
+      <c r="DW6" t="n">
+        <v>168</v>
+      </c>
+      <c r="DX6" t="n">
+        <v>641042</v>
+      </c>
+      <c r="DY6" t="n">
+        <v>273</v>
+      </c>
+      <c r="DZ6" t="n">
+        <v>17846</v>
+      </c>
+      <c r="EA6" t="n">
         <v>5199</v>
       </c>
     </row>

--- a/data/cint_panelbook.xlsx
+++ b/data/cint_panelbook.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EA6"/>
+  <dimension ref="A1:EA7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3069,6 +3069,403 @@
         <v>17846</v>
       </c>
       <c r="EA6" t="n">
+        <v>5199</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2173</v>
+      </c>
+      <c r="C7" t="n">
+        <v>28516</v>
+      </c>
+      <c r="D7" t="n">
+        <v>9493</v>
+      </c>
+      <c r="E7" t="n">
+        <v>780092</v>
+      </c>
+      <c r="F7" t="n">
+        <v>4457673</v>
+      </c>
+      <c r="G7" t="n">
+        <v>865895</v>
+      </c>
+      <c r="H7" t="n">
+        <v>6716</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1496</v>
+      </c>
+      <c r="J7" t="n">
+        <v>14755</v>
+      </c>
+      <c r="K7" t="n">
+        <v>15812</v>
+      </c>
+      <c r="L7" t="n">
+        <v>20282</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1278943</v>
+      </c>
+      <c r="N7" t="n">
+        <v>50</v>
+      </c>
+      <c r="O7" t="n">
+        <v>17533</v>
+      </c>
+      <c r="P7" t="n">
+        <v>20915</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3951</v>
+      </c>
+      <c r="R7" t="n">
+        <v>3595316</v>
+      </c>
+      <c r="S7" t="n">
+        <v>253796</v>
+      </c>
+      <c r="T7" t="n">
+        <v>97</v>
+      </c>
+      <c r="U7" t="n">
+        <v>9639</v>
+      </c>
+      <c r="V7" t="n">
+        <v>5683167</v>
+      </c>
+      <c r="W7" t="n">
+        <v>736724</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2405488</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>729952</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>112207</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>230228</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>9251</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>531470</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2413</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>538220</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>73756</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>146373</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>334641</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>30882</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>90542</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>703</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>15270</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1250397</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>6348389</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>278</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>10912450</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>43566</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>816924</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>117534</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>428</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>29699</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>420736</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>549915</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1292</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>3384498</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1364615</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>8489</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>785595</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>92652</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>5148664</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>20436</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>8467</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>2521220</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>28594</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>54434</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>233666</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>41005</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>98223</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>6097</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>912</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>107</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>352</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>190783</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>9062</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>1870</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>807408</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>3189</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>571</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>3464778</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>11489</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>1138</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>154364</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>8970</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>1880</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>8641</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>3000670</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>508629</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>15341</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>381183</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>302</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>640823</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>19578</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>104474</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>298</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>56991</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>14366</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>479437</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>996816</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>2333142</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>994348</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>46067</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>46099</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>864144</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>1720</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>1201858</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>20980</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>207047</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>217</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>919396</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>255876</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>131073</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>1373616</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>1009355</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>4230879</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>29660</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>233</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>2832982</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>640281</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>459221</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>17588</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>961746</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>16473</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>1127970</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>17511</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>249555</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>746758</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>22982706</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>77339497</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>69906</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>406</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>168</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>641042</v>
+      </c>
+      <c r="DY7" t="n">
+        <v>273</v>
+      </c>
+      <c r="DZ7" t="n">
+        <v>17846</v>
+      </c>
+      <c r="EA7" t="n">
         <v>5199</v>
       </c>
     </row>

--- a/data/cint_panelbook.xlsx
+++ b/data/cint_panelbook.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EA7"/>
+  <dimension ref="A1:EA8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3466,6 +3466,403 @@
         <v>17846</v>
       </c>
       <c r="EA7" t="n">
+        <v>5199</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2173</v>
+      </c>
+      <c r="C8" t="n">
+        <v>28516</v>
+      </c>
+      <c r="D8" t="n">
+        <v>9493</v>
+      </c>
+      <c r="E8" t="n">
+        <v>780092</v>
+      </c>
+      <c r="F8" t="n">
+        <v>4457673</v>
+      </c>
+      <c r="G8" t="n">
+        <v>865895</v>
+      </c>
+      <c r="H8" t="n">
+        <v>6716</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1496</v>
+      </c>
+      <c r="J8" t="n">
+        <v>14755</v>
+      </c>
+      <c r="K8" t="n">
+        <v>15812</v>
+      </c>
+      <c r="L8" t="n">
+        <v>20282</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1278943</v>
+      </c>
+      <c r="N8" t="n">
+        <v>50</v>
+      </c>
+      <c r="O8" t="n">
+        <v>17533</v>
+      </c>
+      <c r="P8" t="n">
+        <v>20915</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3951</v>
+      </c>
+      <c r="R8" t="n">
+        <v>3595316</v>
+      </c>
+      <c r="S8" t="n">
+        <v>253796</v>
+      </c>
+      <c r="T8" t="n">
+        <v>97</v>
+      </c>
+      <c r="U8" t="n">
+        <v>9639</v>
+      </c>
+      <c r="V8" t="n">
+        <v>5683167</v>
+      </c>
+      <c r="W8" t="n">
+        <v>736724</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2405488</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>729952</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>112207</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>230228</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>9251</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>531470</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2413</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>538220</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>73756</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>146373</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>334641</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>30882</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>90542</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>703</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>15270</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1250397</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>6348389</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>278</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>10912450</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>43566</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>816924</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>117534</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>428</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>29699</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>420736</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>549915</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1292</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>3384498</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>1364615</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>8489</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>785595</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>92652</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>5148664</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>20436</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>8467</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>2521220</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>28594</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>54434</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>233666</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>41005</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>98223</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>6097</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>912</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>107</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>352</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>190783</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>9062</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>1870</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>807408</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>3189</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>571</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>3464778</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>11489</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>1138</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>154364</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>8970</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>1880</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>8641</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>3000670</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>508629</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>15341</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>381183</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>302</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>640823</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>19578</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>104474</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>298</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>56991</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>14366</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>479437</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>996816</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>2333142</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>994348</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>46067</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>46099</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>864144</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>1720</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>1201858</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>20980</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>207047</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>217</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>919396</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>255876</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>131073</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>1373616</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>1009355</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>4230879</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>29660</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>233</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>2832982</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>640281</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>459221</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>17588</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>961746</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>16473</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>1127970</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>17511</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>249555</v>
+      </c>
+      <c r="DR8" t="n">
+        <v>746758</v>
+      </c>
+      <c r="DS8" t="n">
+        <v>22982706</v>
+      </c>
+      <c r="DT8" t="n">
+        <v>77339497</v>
+      </c>
+      <c r="DU8" t="n">
+        <v>69906</v>
+      </c>
+      <c r="DV8" t="n">
+        <v>406</v>
+      </c>
+      <c r="DW8" t="n">
+        <v>168</v>
+      </c>
+      <c r="DX8" t="n">
+        <v>641042</v>
+      </c>
+      <c r="DY8" t="n">
+        <v>273</v>
+      </c>
+      <c r="DZ8" t="n">
+        <v>17846</v>
+      </c>
+      <c r="EA8" t="n">
         <v>5199</v>
       </c>
     </row>

--- a/data/cint_panelbook.xlsx
+++ b/data/cint_panelbook.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EA8"/>
+  <dimension ref="A1:EA9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3863,6 +3863,403 @@
         <v>17846</v>
       </c>
       <c r="EA8" t="n">
+        <v>5199</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2173</v>
+      </c>
+      <c r="C9" t="n">
+        <v>28516</v>
+      </c>
+      <c r="D9" t="n">
+        <v>9493</v>
+      </c>
+      <c r="E9" t="n">
+        <v>780092</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4457673</v>
+      </c>
+      <c r="G9" t="n">
+        <v>865895</v>
+      </c>
+      <c r="H9" t="n">
+        <v>6716</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1496</v>
+      </c>
+      <c r="J9" t="n">
+        <v>14755</v>
+      </c>
+      <c r="K9" t="n">
+        <v>15812</v>
+      </c>
+      <c r="L9" t="n">
+        <v>20282</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1278943</v>
+      </c>
+      <c r="N9" t="n">
+        <v>50</v>
+      </c>
+      <c r="O9" t="n">
+        <v>17533</v>
+      </c>
+      <c r="P9" t="n">
+        <v>20915</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3951</v>
+      </c>
+      <c r="R9" t="n">
+        <v>3595316</v>
+      </c>
+      <c r="S9" t="n">
+        <v>253796</v>
+      </c>
+      <c r="T9" t="n">
+        <v>97</v>
+      </c>
+      <c r="U9" t="n">
+        <v>9639</v>
+      </c>
+      <c r="V9" t="n">
+        <v>5683167</v>
+      </c>
+      <c r="W9" t="n">
+        <v>736724</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2405488</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>729952</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>112207</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>230228</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>9251</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>531470</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2413</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>538220</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>73756</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>146373</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>334641</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>30882</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>90542</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>703</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>15270</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1250397</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>6348389</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>278</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>10912450</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>43566</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>816924</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>117534</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>428</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>29699</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>420736</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>549915</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1292</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>3384498</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1364615</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>8489</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>785595</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>92652</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>5148664</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>20436</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>8467</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>2521220</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>28594</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>54434</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>233666</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>41005</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>98223</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>6097</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>912</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>107</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>352</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>190783</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>9062</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>1870</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>807408</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>3189</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>571</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>3464778</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>11489</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>1138</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>154364</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>8970</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>1880</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>8641</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>3000670</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>508629</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>15341</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>381183</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>302</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>640823</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>19578</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>104474</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>298</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>56991</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>14366</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>479437</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>996816</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>2333142</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>994348</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>46067</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>46099</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>864144</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>1720</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>1201858</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>20980</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>207047</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>217</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>919396</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>255876</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>131073</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>1373616</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>1009355</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>4230879</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>29660</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>233</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>2832982</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>640281</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>459221</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>17588</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>961746</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>16473</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>1127970</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>17511</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>249555</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>746758</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>22982706</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>77339497</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>69906</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>406</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>168</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>641042</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>273</v>
+      </c>
+      <c r="DZ9" t="n">
+        <v>17846</v>
+      </c>
+      <c r="EA9" t="n">
         <v>5199</v>
       </c>
     </row>

--- a/data/cint_panelbook.xlsx
+++ b/data/cint_panelbook.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EA9"/>
+  <dimension ref="A1:EA10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4260,6 +4260,403 @@
         <v>17846</v>
       </c>
       <c r="EA9" t="n">
+        <v>5199</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2173</v>
+      </c>
+      <c r="C10" t="n">
+        <v>28516</v>
+      </c>
+      <c r="D10" t="n">
+        <v>9493</v>
+      </c>
+      <c r="E10" t="n">
+        <v>780092</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4457673</v>
+      </c>
+      <c r="G10" t="n">
+        <v>865895</v>
+      </c>
+      <c r="H10" t="n">
+        <v>6716</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1496</v>
+      </c>
+      <c r="J10" t="n">
+        <v>14755</v>
+      </c>
+      <c r="K10" t="n">
+        <v>15812</v>
+      </c>
+      <c r="L10" t="n">
+        <v>20282</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1278943</v>
+      </c>
+      <c r="N10" t="n">
+        <v>50</v>
+      </c>
+      <c r="O10" t="n">
+        <v>17533</v>
+      </c>
+      <c r="P10" t="n">
+        <v>20915</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3951</v>
+      </c>
+      <c r="R10" t="n">
+        <v>3595316</v>
+      </c>
+      <c r="S10" t="n">
+        <v>253796</v>
+      </c>
+      <c r="T10" t="n">
+        <v>97</v>
+      </c>
+      <c r="U10" t="n">
+        <v>9639</v>
+      </c>
+      <c r="V10" t="n">
+        <v>5683167</v>
+      </c>
+      <c r="W10" t="n">
+        <v>736724</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2405488</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>729952</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>112207</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>230228</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>9251</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>531470</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2413</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>538220</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>73756</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>146373</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>334641</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>30882</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>90542</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>703</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>15270</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1250397</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>6348389</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>278</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>10912450</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>43566</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>816924</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>117534</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>428</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>29699</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>420736</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>549915</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1292</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>3384498</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1364615</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>8489</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>785595</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>92652</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>5148664</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>20436</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>8467</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>2521220</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>28594</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>54434</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>233666</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>41005</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>98223</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>6097</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>912</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>107</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>352</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>190783</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>9062</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>1870</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>807408</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>3189</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>571</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>3464778</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>11489</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>1138</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>154364</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>8970</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>1880</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>8641</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>3000670</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>508629</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>15341</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>381183</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>302</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>640823</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>19578</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>104474</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>298</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>56991</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>14366</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>479437</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>996816</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>2333142</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>994348</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>46067</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>46099</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>864144</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>1720</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>1201858</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>20980</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>207047</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>217</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>919396</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>255876</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>131073</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>1373616</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>1009355</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>4230879</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>29660</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>233</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>2832982</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>640281</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>459221</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>17588</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>961746</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>16473</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>1127970</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>17511</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>249555</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>746758</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>22982706</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>77339497</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>69906</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>406</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>168</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>641042</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>273</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>17846</v>
+      </c>
+      <c r="EA10" t="n">
         <v>5199</v>
       </c>
     </row>

--- a/data/cint_panelbook.xlsx
+++ b/data/cint_panelbook.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EA10"/>
+  <dimension ref="A1:EA11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4657,6 +4657,403 @@
         <v>17846</v>
       </c>
       <c r="EA10" t="n">
+        <v>5199</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2173</v>
+      </c>
+      <c r="C11" t="n">
+        <v>28516</v>
+      </c>
+      <c r="D11" t="n">
+        <v>9493</v>
+      </c>
+      <c r="E11" t="n">
+        <v>780092</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4457673</v>
+      </c>
+      <c r="G11" t="n">
+        <v>865895</v>
+      </c>
+      <c r="H11" t="n">
+        <v>6716</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1496</v>
+      </c>
+      <c r="J11" t="n">
+        <v>14755</v>
+      </c>
+      <c r="K11" t="n">
+        <v>15812</v>
+      </c>
+      <c r="L11" t="n">
+        <v>20282</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1278943</v>
+      </c>
+      <c r="N11" t="n">
+        <v>50</v>
+      </c>
+      <c r="O11" t="n">
+        <v>17533</v>
+      </c>
+      <c r="P11" t="n">
+        <v>20915</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3951</v>
+      </c>
+      <c r="R11" t="n">
+        <v>3595316</v>
+      </c>
+      <c r="S11" t="n">
+        <v>253796</v>
+      </c>
+      <c r="T11" t="n">
+        <v>97</v>
+      </c>
+      <c r="U11" t="n">
+        <v>9639</v>
+      </c>
+      <c r="V11" t="n">
+        <v>5683167</v>
+      </c>
+      <c r="W11" t="n">
+        <v>736724</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2405488</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>729952</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>112207</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>230228</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>9251</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>531470</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2413</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>538220</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>73756</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>146373</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>334641</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>30882</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>90542</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>703</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>15270</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1250397</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>6348389</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>278</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>10912450</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>43566</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>816924</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>117534</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>428</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>29699</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>420736</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>549915</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1292</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>3384498</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1364615</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>8489</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>785595</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>92652</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>5148664</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>20436</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>8467</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>2521220</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>28594</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>54434</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>233666</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>41005</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>98223</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>6097</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>912</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>107</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>352</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>190783</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>9062</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>1870</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>807408</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>3189</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>571</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>3464778</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>11489</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>1138</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>154364</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>8970</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>1880</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>8641</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>3000670</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>508629</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>15341</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>381183</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>302</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>640823</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>19578</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>104474</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>298</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>56991</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>14366</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>479437</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>996816</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>2333142</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>994348</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>46067</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>46099</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>864144</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>1720</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>1201858</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>20980</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>207047</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>217</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>919396</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>255876</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>131073</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>1373616</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>1009355</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>4230879</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>29660</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>233</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>2832982</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>640281</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>459221</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>17588</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>961746</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>16473</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>1127970</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>17511</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>249555</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>746758</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>22982706</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>77339497</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>69906</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>406</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>168</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>641042</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>273</v>
+      </c>
+      <c r="DZ11" t="n">
+        <v>17846</v>
+      </c>
+      <c r="EA11" t="n">
         <v>5199</v>
       </c>
     </row>

--- a/data/cint_panelbook.xlsx
+++ b/data/cint_panelbook.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EA11"/>
+  <dimension ref="A1:EA12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5054,6 +5054,403 @@
         <v>17846</v>
       </c>
       <c r="EA11" t="n">
+        <v>5199</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2173</v>
+      </c>
+      <c r="C12" t="n">
+        <v>28516</v>
+      </c>
+      <c r="D12" t="n">
+        <v>9493</v>
+      </c>
+      <c r="E12" t="n">
+        <v>780092</v>
+      </c>
+      <c r="F12" t="n">
+        <v>4457673</v>
+      </c>
+      <c r="G12" t="n">
+        <v>865895</v>
+      </c>
+      <c r="H12" t="n">
+        <v>6716</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1496</v>
+      </c>
+      <c r="J12" t="n">
+        <v>14755</v>
+      </c>
+      <c r="K12" t="n">
+        <v>15812</v>
+      </c>
+      <c r="L12" t="n">
+        <v>20282</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1278943</v>
+      </c>
+      <c r="N12" t="n">
+        <v>50</v>
+      </c>
+      <c r="O12" t="n">
+        <v>17533</v>
+      </c>
+      <c r="P12" t="n">
+        <v>20915</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3951</v>
+      </c>
+      <c r="R12" t="n">
+        <v>3595316</v>
+      </c>
+      <c r="S12" t="n">
+        <v>253796</v>
+      </c>
+      <c r="T12" t="n">
+        <v>97</v>
+      </c>
+      <c r="U12" t="n">
+        <v>9639</v>
+      </c>
+      <c r="V12" t="n">
+        <v>5683167</v>
+      </c>
+      <c r="W12" t="n">
+        <v>736724</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2405488</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>729952</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>112207</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>230228</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>9251</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>531470</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2413</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>538220</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>73756</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>146373</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>334641</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>30882</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>90542</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>703</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>15270</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1250397</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>6348389</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>278</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>10912450</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>43566</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>816924</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>117534</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>428</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>29699</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>420736</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>549915</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1292</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>3384498</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1364615</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>8489</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>785595</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>92652</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>5148664</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>20436</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>8467</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>2521220</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>28594</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>54434</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>233666</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>41005</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>98223</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>6097</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>912</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>107</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>352</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>190783</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>9062</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>1870</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>807408</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>3189</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>571</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>3464778</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>11489</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>1138</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>154364</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>8970</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>1880</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>8641</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>3000670</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>508629</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>15341</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>381183</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>302</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>640823</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>19578</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>104474</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>298</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>56991</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>14366</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>479437</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>996816</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>2333142</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>994348</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>46067</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>46099</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>864144</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>1720</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>1201858</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>20980</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>207047</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>217</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>919396</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>255876</v>
+      </c>
+      <c r="DC12" t="n">
+        <v>131073</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>1373616</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>1009355</v>
+      </c>
+      <c r="DF12" t="n">
+        <v>4230879</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>29660</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>233</v>
+      </c>
+      <c r="DI12" t="n">
+        <v>2832982</v>
+      </c>
+      <c r="DJ12" t="n">
+        <v>640281</v>
+      </c>
+      <c r="DK12" t="n">
+        <v>459221</v>
+      </c>
+      <c r="DL12" t="n">
+        <v>17588</v>
+      </c>
+      <c r="DM12" t="n">
+        <v>961746</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>16473</v>
+      </c>
+      <c r="DO12" t="n">
+        <v>1127970</v>
+      </c>
+      <c r="DP12" t="n">
+        <v>17511</v>
+      </c>
+      <c r="DQ12" t="n">
+        <v>249555</v>
+      </c>
+      <c r="DR12" t="n">
+        <v>746758</v>
+      </c>
+      <c r="DS12" t="n">
+        <v>22982706</v>
+      </c>
+      <c r="DT12" t="n">
+        <v>77339497</v>
+      </c>
+      <c r="DU12" t="n">
+        <v>69906</v>
+      </c>
+      <c r="DV12" t="n">
+        <v>406</v>
+      </c>
+      <c r="DW12" t="n">
+        <v>168</v>
+      </c>
+      <c r="DX12" t="n">
+        <v>641042</v>
+      </c>
+      <c r="DY12" t="n">
+        <v>273</v>
+      </c>
+      <c r="DZ12" t="n">
+        <v>17846</v>
+      </c>
+      <c r="EA12" t="n">
         <v>5199</v>
       </c>
     </row>
